--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.72918132502291</v>
+        <v>4.830991965316223</v>
       </c>
       <c r="D2" t="n">
-        <v>28.6111676380765</v>
+        <v>4.649314741187431</v>
       </c>
       <c r="E2" t="n">
-        <v>15.81331460631751</v>
+        <v>2.569663623526596</v>
       </c>
       <c r="F2" t="n">
-        <v>18.49981847183056</v>
+        <v>3.006220501672466</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.70682116573129</v>
+        <v>7.589858439431335</v>
       </c>
       <c r="D3" t="n">
-        <v>11.43555749881228</v>
+        <v>1.858278093556996</v>
       </c>
       <c r="E3" t="n">
-        <v>15.81331460631751</v>
+        <v>2.569663623526596</v>
       </c>
       <c r="F3" t="n">
-        <v>18.49981847183056</v>
+        <v>3.006220501672466</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.99159470306934</v>
+        <v>3.573634139248767</v>
       </c>
       <c r="D4" t="n">
-        <v>21.47002493116427</v>
+        <v>3.488879051314194</v>
       </c>
       <c r="E4" t="n">
-        <v>15.81331460631751</v>
+        <v>2.569663623526596</v>
       </c>
       <c r="F4" t="n">
-        <v>18.49981847183056</v>
+        <v>3.006220501672466</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>66.86110677181074</v>
+        <v>10.86492985041925</v>
       </c>
       <c r="D5" t="n">
-        <v>66.14155362152218</v>
+        <v>10.74800246349735</v>
       </c>
       <c r="E5" t="n">
-        <v>15.81331460631751</v>
+        <v>2.569663623526596</v>
       </c>
       <c r="F5" t="n">
-        <v>18.49981847183056</v>
+        <v>3.006220501672466</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.58974313649879</v>
+        <v>5.295833259681054</v>
       </c>
       <c r="D6" t="n">
-        <v>31.26355005683309</v>
+        <v>5.080326884235378</v>
       </c>
       <c r="E6" t="n">
-        <v>15.81331460631751</v>
+        <v>2.569663623526596</v>
       </c>
       <c r="F6" t="n">
-        <v>18.49981847183056</v>
+        <v>3.006220501672466</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
